--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/89.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/89.xlsx
@@ -426,13 +426,13 @@
         <v>-12.52276583901049</v>
       </c>
       <c r="E2">
-        <v>-8.742157749879119</v>
+        <v>-11.20211992879982</v>
       </c>
       <c r="F2">
-        <v>5.36618492693302</v>
+        <v>4.061368039496544</v>
       </c>
       <c r="G2">
-        <v>-16.55623471475036</v>
+        <v>-15.90717246686639</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.37190827001114</v>
       </c>
       <c r="E3">
-        <v>-10.30744743300042</v>
+        <v>-10.3569708247483</v>
       </c>
       <c r="F3">
-        <v>5.47017580845852</v>
+        <v>3.836614830801039</v>
       </c>
       <c r="G3">
-        <v>-15.31651486338624</v>
+        <v>-15.75062338940533</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.03125992974092</v>
       </c>
       <c r="E4">
-        <v>-10.92417125115703</v>
+        <v>-10.38111211968319</v>
       </c>
       <c r="F4">
-        <v>5.275419573507354</v>
+        <v>4.259975847234059</v>
       </c>
       <c r="G4">
-        <v>-15.05228863698762</v>
+        <v>-14.5557746722805</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.641855561713443</v>
       </c>
       <c r="E5">
-        <v>-10.05583183171223</v>
+        <v>-11.57488579521521</v>
       </c>
       <c r="F5">
-        <v>5.387685318441026</v>
+        <v>4.633758949984246</v>
       </c>
       <c r="G5">
-        <v>-14.30872024559408</v>
+        <v>-14.9678862784639</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.209710544333507</v>
       </c>
       <c r="E6">
-        <v>-11.45093240467726</v>
+        <v>-14.21188866546578</v>
       </c>
       <c r="F6">
-        <v>5.435028623077172</v>
+        <v>4.079767534822119</v>
       </c>
       <c r="G6">
-        <v>-13.21506000814983</v>
+        <v>-12.52196750459356</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.773315337696852</v>
       </c>
       <c r="E7">
-        <v>-12.58220408195541</v>
+        <v>-13.42043367772321</v>
       </c>
       <c r="F7">
-        <v>5.672658944571115</v>
+        <v>4.549969821116091</v>
       </c>
       <c r="G7">
-        <v>-12.68058236247112</v>
+        <v>-13.86675413973752</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.348871049239036</v>
       </c>
       <c r="E8">
-        <v>-14.3593176652595</v>
+        <v>-16.74857677949844</v>
       </c>
       <c r="F8">
-        <v>5.528902791214846</v>
+        <v>4.481721598396144</v>
       </c>
       <c r="G8">
-        <v>-11.46156997345514</v>
+        <v>-11.63778038087393</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.951018371817764</v>
       </c>
       <c r="E9">
-        <v>-14.26820023975116</v>
+        <v>-15.66570996088828</v>
       </c>
       <c r="F9">
-        <v>5.559590260738316</v>
+        <v>4.855507868558162</v>
       </c>
       <c r="G9">
-        <v>-10.46288763225982</v>
+        <v>-10.18960540853852</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.591101911637824</v>
       </c>
       <c r="E10">
-        <v>-15.88726102323954</v>
+        <v>-15.35281504932829</v>
       </c>
       <c r="F10">
-        <v>5.35411075303371</v>
+        <v>4.547168245351679</v>
       </c>
       <c r="G10">
-        <v>-9.503375665885157</v>
+        <v>-9.122997293968437</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.2730051899512307</v>
       </c>
       <c r="E11">
-        <v>-16.17969628923287</v>
+        <v>-17.84453541646478</v>
       </c>
       <c r="F11">
-        <v>5.820469385070909</v>
+        <v>4.739490324310815</v>
       </c>
       <c r="G11">
-        <v>-7.804254720581916</v>
+        <v>-8.433112709039714</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.9924570228637175</v>
       </c>
       <c r="E12">
-        <v>-17.27498018357207</v>
+        <v>-17.83969900622459</v>
       </c>
       <c r="F12">
-        <v>5.590146282670805</v>
+        <v>4.748604551854168</v>
       </c>
       <c r="G12">
-        <v>-7.819489851153642</v>
+        <v>-7.578273571525726</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.206099869125914</v>
       </c>
       <c r="E13">
-        <v>-18.08172782803854</v>
+        <v>-18.2702753718219</v>
       </c>
       <c r="F13">
-        <v>6.052366691150961</v>
+        <v>4.822874024464617</v>
       </c>
       <c r="G13">
-        <v>-6.612507984627378</v>
+        <v>-7.328324072765212</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.359291374924525</v>
       </c>
       <c r="E14">
-        <v>-18.72771011675871</v>
+        <v>-19.83376725076216</v>
       </c>
       <c r="F14">
-        <v>5.712292768810903</v>
+        <v>4.530401550824921</v>
       </c>
       <c r="G14">
-        <v>-6.396683589285671</v>
+        <v>-7.164134256199518</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.456891548829786</v>
       </c>
       <c r="E15">
-        <v>-19.96344916091981</v>
+        <v>-20.68570000887717</v>
       </c>
       <c r="F15">
-        <v>5.784267451549879</v>
+        <v>5.11220442556808</v>
       </c>
       <c r="G15">
-        <v>-4.583653393067188</v>
+        <v>-4.919494995844093</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.493724801147938</v>
       </c>
       <c r="E16">
-        <v>-20.31528442047176</v>
+        <v>-22.17782313745653</v>
       </c>
       <c r="F16">
-        <v>6.252391915682795</v>
+        <v>5.246391827783264</v>
       </c>
       <c r="G16">
-        <v>-4.291120347035029</v>
+        <v>-3.890133829136345</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.470256706437899</v>
       </c>
       <c r="E17">
-        <v>-21.90596978582807</v>
+        <v>-24.1405996266011</v>
       </c>
       <c r="F17">
-        <v>5.824770730337243</v>
+        <v>5.365616376509377</v>
       </c>
       <c r="G17">
-        <v>-4.056478810848104</v>
+        <v>-4.102303382202696</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.37481247950199</v>
       </c>
       <c r="E18">
-        <v>-22.61878782242744</v>
+        <v>-23.56921036173527</v>
       </c>
       <c r="F18">
-        <v>5.954493665576804</v>
+        <v>5.28306095454935</v>
       </c>
       <c r="G18">
-        <v>-2.974102567874469</v>
+        <v>-3.968547410779523</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.193295286376893</v>
       </c>
       <c r="E19">
-        <v>-24.01752928849464</v>
+        <v>-24.00449181182656</v>
       </c>
       <c r="F19">
-        <v>5.969968056076563</v>
+        <v>5.612259568368086</v>
       </c>
       <c r="G19">
-        <v>-2.856962224512897</v>
+        <v>-3.265586170970679</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.903136937687599</v>
       </c>
       <c r="E20">
-        <v>-24.37932266238945</v>
+        <v>-26.22008394787134</v>
       </c>
       <c r="F20">
-        <v>6.35847487272259</v>
+        <v>5.671040397125537</v>
       </c>
       <c r="G20">
-        <v>-2.763095016292402</v>
+        <v>-3.605390496758091</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>9.480478772357555</v>
       </c>
       <c r="E21">
-        <v>-25.55211138936992</v>
+        <v>-26.76422991310702</v>
       </c>
       <c r="F21">
-        <v>6.151577948223666</v>
+        <v>5.176742025328153</v>
       </c>
       <c r="G21">
-        <v>-1.724116714793072</v>
+        <v>-2.150392490066248</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>9.904215049818438</v>
       </c>
       <c r="E22">
-        <v>-25.76329224624362</v>
+        <v>-26.9598147054983</v>
       </c>
       <c r="F22">
-        <v>6.380607162890857</v>
+        <v>5.046365019545516</v>
       </c>
       <c r="G22">
-        <v>-1.920276469631507</v>
+        <v>-1.412213666810637</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>10.15729897963384</v>
       </c>
       <c r="E23">
-        <v>-25.82229826256357</v>
+        <v>-26.84424804882255</v>
       </c>
       <c r="F23">
-        <v>5.940523795696713</v>
+        <v>5.328518065440208</v>
       </c>
       <c r="G23">
-        <v>-1.5751785815268</v>
+        <v>-2.286684339372503</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>10.23544908866038</v>
       </c>
       <c r="E24">
-        <v>-25.89968082640664</v>
+        <v>-27.4919873854577</v>
       </c>
       <c r="F24">
-        <v>6.151796499639997</v>
+        <v>5.127913204543324</v>
       </c>
       <c r="G24">
-        <v>-0.5940785476905485</v>
+        <v>-1.746184811357854</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>10.13993065904345</v>
       </c>
       <c r="E25">
-        <v>-26.50331282620708</v>
+        <v>-28.51738334043652</v>
       </c>
       <c r="F25">
-        <v>5.56070360599687</v>
+        <v>4.830817893336461</v>
       </c>
       <c r="G25">
-        <v>-0.3083288094683559</v>
+        <v>-1.321882121226083</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>9.888429500856308</v>
       </c>
       <c r="E26">
-        <v>-27.07846978144728</v>
+        <v>-30.4321738547588</v>
       </c>
       <c r="F26">
-        <v>5.604706874857355</v>
+        <v>4.920566507564414</v>
       </c>
       <c r="G26">
-        <v>-0.5029855766319624</v>
+        <v>-0.8774777985798584</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>9.499383979554755</v>
       </c>
       <c r="E27">
-        <v>-27.80560685285891</v>
+        <v>-26.59627334063653</v>
       </c>
       <c r="F27">
-        <v>5.439679967350818</v>
+        <v>4.989611334359828</v>
       </c>
       <c r="G27">
-        <v>0.23123383415868</v>
+        <v>-0.5239711248054025</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.005979591159511</v>
       </c>
       <c r="E28">
-        <v>-27.03216613471885</v>
+        <v>-27.23164088628272</v>
       </c>
       <c r="F28">
-        <v>5.415861030382609</v>
+        <v>4.655740788090545</v>
       </c>
       <c r="G28">
-        <v>-0.455614980510531</v>
+        <v>-0.7395538503227422</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.435793749985997</v>
       </c>
       <c r="E29">
-        <v>-26.60103276681859</v>
+        <v>-28.27616964394395</v>
       </c>
       <c r="F29">
-        <v>5.466528533735263</v>
+        <v>4.589104777992516</v>
       </c>
       <c r="G29">
-        <v>0.3426370021006947</v>
+        <v>0.3230187092349736</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.828805143338295</v>
       </c>
       <c r="E30">
-        <v>-26.40032627032464</v>
+        <v>-27.67685780834683</v>
       </c>
       <c r="F30">
-        <v>5.695136482628947</v>
+        <v>3.97911668907228</v>
       </c>
       <c r="G30">
-        <v>0.6465483931513289</v>
+        <v>-0.03456655664386438</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.211606112444034</v>
       </c>
       <c r="E31">
-        <v>-26.77051543502967</v>
+        <v>-28.3695377210341</v>
       </c>
       <c r="F31">
-        <v>5.158543660653838</v>
+        <v>4.630995383161804</v>
       </c>
       <c r="G31">
-        <v>-0.2707640492342457</v>
+        <v>-1.239658101667205</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.618459378002156</v>
       </c>
       <c r="E32">
-        <v>-26.38769635631724</v>
+        <v>-26.31177648957865</v>
       </c>
       <c r="F32">
-        <v>5.381690991551087</v>
+        <v>4.362905645796214</v>
       </c>
       <c r="G32">
-        <v>-0.9068688218775079</v>
+        <v>0.4935316677806754</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.063818380545356</v>
       </c>
       <c r="E33">
-        <v>-25.25774246497532</v>
+        <v>-27.26670938899812</v>
       </c>
       <c r="F33">
-        <v>5.096117140879046</v>
+        <v>4.76976286288444</v>
       </c>
       <c r="G33">
-        <v>-0.6975397168838515</v>
+        <v>-0.2200696653913861</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.567779037268482</v>
       </c>
       <c r="E34">
-        <v>-25.76432473831737</v>
+        <v>-27.07164084264371</v>
       </c>
       <c r="F34">
-        <v>5.770498712321049</v>
+        <v>4.415418166540356</v>
       </c>
       <c r="G34">
-        <v>-0.004900758066455271</v>
+        <v>-0.02383376800554719</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.129586934030538</v>
       </c>
       <c r="E35">
-        <v>-24.40186540599963</v>
+        <v>-26.03421726070052</v>
       </c>
       <c r="F35">
-        <v>5.66395489685986</v>
+        <v>4.617202888344242</v>
       </c>
       <c r="G35">
-        <v>-0.4732932936902391</v>
+        <v>-1.445103936743296</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.754397097838868</v>
       </c>
       <c r="E36">
-        <v>-23.8038487139687</v>
+        <v>-26.52025837594378</v>
       </c>
       <c r="F36">
-        <v>6.165219990979261</v>
+        <v>4.832464947488518</v>
       </c>
       <c r="G36">
-        <v>-1.12666587186634</v>
+        <v>-1.825174427924864</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.428897248293326</v>
       </c>
       <c r="E37">
-        <v>-23.38342065862258</v>
+        <v>-25.22799039074492</v>
       </c>
       <c r="F37">
-        <v>5.876849315660554</v>
+        <v>4.563290371570853</v>
       </c>
       <c r="G37">
-        <v>-1.257905828679668</v>
+        <v>-2.132849909253649</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.147484307315818</v>
       </c>
       <c r="E38">
-        <v>-23.41391993106424</v>
+        <v>-24.23745010020314</v>
       </c>
       <c r="F38">
-        <v>6.349181686410792</v>
+        <v>4.999045470498101</v>
       </c>
       <c r="G38">
-        <v>-1.376598817899158</v>
+        <v>-1.70786193619525</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.890970328477148</v>
       </c>
       <c r="E39">
-        <v>-23.02486967211727</v>
+        <v>-23.84711375463799</v>
       </c>
       <c r="F39">
-        <v>6.176136475854386</v>
+        <v>5.158209498705681</v>
       </c>
       <c r="G39">
-        <v>-1.332886374598621</v>
+        <v>-1.548949129219155</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.649923302680777</v>
       </c>
       <c r="E40">
-        <v>-22.36652012088215</v>
+        <v>-22.83444734009473</v>
       </c>
       <c r="F40">
-        <v>6.290573481598124</v>
+        <v>5.471282818893412</v>
       </c>
       <c r="G40">
-        <v>-1.706041136148651</v>
+        <v>-1.627137593765662</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.406324244297892</v>
       </c>
       <c r="E41">
-        <v>-21.85119336423129</v>
+        <v>-23.20245830880207</v>
       </c>
       <c r="F41">
-        <v>6.559258692387919</v>
+        <v>5.471552048899037</v>
       </c>
       <c r="G41">
-        <v>-1.676206499748739</v>
+        <v>-2.975532723547434</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.153093115787725</v>
       </c>
       <c r="E42">
-        <v>-20.58965107517448</v>
+        <v>-20.77476150718602</v>
       </c>
       <c r="F42">
-        <v>6.461944715001912</v>
+        <v>5.931229025678999</v>
       </c>
       <c r="G42">
-        <v>-2.364485470090915</v>
+        <v>-2.913178598315261</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.877400428934927</v>
       </c>
       <c r="E43">
-        <v>-20.84567741014614</v>
+        <v>-20.04448620328708</v>
       </c>
       <c r="F43">
-        <v>6.584789615450719</v>
+        <v>5.46476903646321</v>
       </c>
       <c r="G43">
-        <v>-3.519438802921993</v>
+        <v>-2.291703126410038</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.576819195271668</v>
       </c>
       <c r="E44">
-        <v>-19.17323950352935</v>
+        <v>-19.32809067222164</v>
       </c>
       <c r="F44">
-        <v>6.601542056624237</v>
+        <v>5.842934253481419</v>
       </c>
       <c r="G44">
-        <v>-3.311304804868014</v>
+        <v>-3.100082067825895</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.24446145458684</v>
       </c>
       <c r="E45">
-        <v>-18.52334914174056</v>
+        <v>-19.58951041973643</v>
       </c>
       <c r="F45">
-        <v>6.566581748540911</v>
+        <v>5.739600609910825</v>
       </c>
       <c r="G45">
-        <v>-3.883562396240892</v>
+        <v>-3.035158959255247</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.882732353596642</v>
       </c>
       <c r="E46">
-        <v>-17.61992763415834</v>
+        <v>-18.41772248551165</v>
       </c>
       <c r="F46">
-        <v>7.043160034850443</v>
+        <v>5.827337917626171</v>
       </c>
       <c r="G46">
-        <v>-3.334071426541582</v>
+        <v>-4.03224561750064</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.489324970388945</v>
       </c>
       <c r="E47">
-        <v>-17.59833587008977</v>
+        <v>-17.23010300615605</v>
       </c>
       <c r="F47">
-        <v>6.915139583469979</v>
+        <v>6.091780380268503</v>
       </c>
       <c r="G47">
-        <v>-3.727417205335628</v>
+        <v>-4.108037247076714</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.069498449261401</v>
       </c>
       <c r="E48">
-        <v>-17.43397943445538</v>
+        <v>-16.99213169705298</v>
       </c>
       <c r="F48">
-        <v>7.231549772021542</v>
+        <v>6.275694564522571</v>
       </c>
       <c r="G48">
-        <v>-4.870214214946502</v>
+        <v>-5.198239619705188</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.6239363404939035</v>
       </c>
       <c r="E49">
-        <v>-15.8250126195301</v>
+        <v>-17.13026373970894</v>
       </c>
       <c r="F49">
-        <v>7.457151847087722</v>
+        <v>6.04111604432768</v>
       </c>
       <c r="G49">
-        <v>-5.030901474331647</v>
+        <v>-5.009667635242761</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.160661051245962</v>
       </c>
       <c r="E50">
-        <v>-16.1158946189388</v>
+        <v>-16.84381964482776</v>
       </c>
       <c r="F50">
-        <v>7.436677697012921</v>
+        <v>5.88344861821019</v>
       </c>
       <c r="G50">
-        <v>-5.246047207837803</v>
+        <v>-5.37052040956886</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3181464253089695</v>
       </c>
       <c r="E51">
-        <v>-14.6816091603854</v>
+        <v>-16.51561396264785</v>
       </c>
       <c r="F51">
-        <v>7.718425314193261</v>
+        <v>6.172303907539022</v>
       </c>
       <c r="G51">
-        <v>-6.146207713784413</v>
+        <v>-5.613868680524067</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.8045082552093418</v>
       </c>
       <c r="E52">
-        <v>-14.35561337352123</v>
+        <v>-15.38018967470466</v>
       </c>
       <c r="F52">
-        <v>7.527686941149565</v>
+        <v>6.639956427309136</v>
       </c>
       <c r="G52">
-        <v>-5.884419704175466</v>
+        <v>-5.016209273228362</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.297838366696078</v>
       </c>
       <c r="E53">
-        <v>-13.97092403504364</v>
+        <v>-14.37488655889787</v>
       </c>
       <c r="F53">
-        <v>7.447583095946637</v>
+        <v>6.783981810671031</v>
       </c>
       <c r="G53">
-        <v>-5.853396581926956</v>
+        <v>-5.434887346488909</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.790932011297163</v>
       </c>
       <c r="E54">
-        <v>-13.08195288801989</v>
+        <v>-13.78680081036577</v>
       </c>
       <c r="F54">
-        <v>7.479572371732599</v>
+        <v>6.462008063238529</v>
       </c>
       <c r="G54">
-        <v>-7.02072142343829</v>
+        <v>-7.384639762933753</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.282914514058266</v>
       </c>
       <c r="E55">
-        <v>-13.49476857855912</v>
+        <v>-13.87641478250356</v>
       </c>
       <c r="F55">
-        <v>7.621779660703568</v>
+        <v>6.62383905220771</v>
       </c>
       <c r="G55">
-        <v>-6.290027743646972</v>
+        <v>-6.600126544310504</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.766039451213307</v>
       </c>
       <c r="E56">
-        <v>-12.20439802396948</v>
+        <v>-13.31912718569762</v>
       </c>
       <c r="F56">
-        <v>7.621193689514856</v>
+        <v>6.695362378760786</v>
       </c>
       <c r="G56">
-        <v>-7.452254345027828</v>
+        <v>-6.497026224580981</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.239093513650525</v>
       </c>
       <c r="E57">
-        <v>-11.72551642613235</v>
+        <v>-12.75882815367658</v>
       </c>
       <c r="F57">
-        <v>8.119313543686195</v>
+        <v>6.493872226257171</v>
       </c>
       <c r="G57">
-        <v>-6.882751127543624</v>
+        <v>-6.752666551123502</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.694037230756749</v>
       </c>
       <c r="E58">
-        <v>-11.34795490574284</v>
+        <v>-12.42832653517478</v>
       </c>
       <c r="F58">
-        <v>7.829807351226116</v>
+        <v>6.415353670675598</v>
       </c>
       <c r="G58">
-        <v>-7.587298118665779</v>
+        <v>-6.856869282517602</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.129092509106948</v>
       </c>
       <c r="E59">
-        <v>-10.74224886484689</v>
+        <v>-11.02504753815189</v>
       </c>
       <c r="F59">
-        <v>7.990355538403791</v>
+        <v>6.398501456029408</v>
       </c>
       <c r="G59">
-        <v>-8.21690760096099</v>
+        <v>-8.299313700524529</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.535446422702813</v>
       </c>
       <c r="E60">
-        <v>-11.15304032750469</v>
+        <v>-12.59542722605781</v>
       </c>
       <c r="F60">
-        <v>8.099865635044598</v>
+        <v>6.638578603162704</v>
       </c>
       <c r="G60">
-        <v>-8.734504774934962</v>
+        <v>-7.528645183346511</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.910043120598914</v>
       </c>
       <c r="E61">
-        <v>-10.71451196154991</v>
+        <v>-10.62678183459931</v>
       </c>
       <c r="F61">
-        <v>7.539341432981283</v>
+        <v>6.161480861312909</v>
       </c>
       <c r="G61">
-        <v>-8.490613574511315</v>
+        <v>-7.675444704194414</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.243093035309917</v>
       </c>
       <c r="E62">
-        <v>-10.77220924888163</v>
+        <v>-11.33212336061202</v>
       </c>
       <c r="F62">
-        <v>8.162599393766985</v>
+        <v>6.732036256644617</v>
       </c>
       <c r="G62">
-        <v>-8.923348224131608</v>
+        <v>-8.491351826166573</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.531140163171739</v>
       </c>
       <c r="E63">
-        <v>-10.21996637212024</v>
+        <v>-10.05598579982849</v>
       </c>
       <c r="F63">
-        <v>7.779554778823307</v>
+        <v>6.941381590488811</v>
       </c>
       <c r="G63">
-        <v>-9.270343054830319</v>
+        <v>-8.767659888510764</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.765912714102163</v>
       </c>
       <c r="E64">
-        <v>-8.518632272860511</v>
+        <v>-9.351101649690552</v>
       </c>
       <c r="F64">
-        <v>7.769339875668723</v>
+        <v>7.128905040524165</v>
       </c>
       <c r="G64">
-        <v>-9.270349675921397</v>
+        <v>-8.941536361324365</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.946107749756413</v>
       </c>
       <c r="E65">
-        <v>-8.87253251655995</v>
+        <v>-9.801834253096006</v>
       </c>
       <c r="F65">
-        <v>7.7280099023935</v>
+        <v>6.477799194921376</v>
       </c>
       <c r="G65">
-        <v>-9.857547759313006</v>
+        <v>-8.433033255946771</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.067361714140983</v>
       </c>
       <c r="E66">
-        <v>-8.762794005932074</v>
+        <v>-7.684274522369271</v>
       </c>
       <c r="F66">
-        <v>7.497015308685248</v>
+        <v>6.39852837902997</v>
       </c>
       <c r="G66">
-        <v>-9.161687639685899</v>
+        <v>-8.874540851246135</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.132751313900898</v>
       </c>
       <c r="E67">
-        <v>-7.918921931550718</v>
+        <v>-9.631269279597102</v>
       </c>
       <c r="F67">
-        <v>7.313055196959633</v>
+        <v>6.219593366174044</v>
       </c>
       <c r="G67">
-        <v>-10.51147981968524</v>
+        <v>-8.463122804353207</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.142649780342236</v>
       </c>
       <c r="E68">
-        <v>-7.732901276263635</v>
+        <v>-8.457819395411505</v>
       </c>
       <c r="F68">
-        <v>7.691495978807128</v>
+        <v>6.064523217757875</v>
       </c>
       <c r="G68">
-        <v>-9.980756332648062</v>
+        <v>-9.728141844728434</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.10261606414452</v>
       </c>
       <c r="E69">
-        <v>-7.493313301939819</v>
+        <v>-8.052960233703752</v>
       </c>
       <c r="F69">
-        <v>7.203142839016305</v>
+        <v>6.061862591819937</v>
       </c>
       <c r="G69">
-        <v>-9.899962468762148</v>
+        <v>-9.229888188340425</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.014233357734829</v>
       </c>
       <c r="E70">
-        <v>-7.956136930945752</v>
+        <v>-6.722829677326769</v>
       </c>
       <c r="F70">
-        <v>7.304431918250065</v>
+        <v>6.08466954070818</v>
       </c>
       <c r="G70">
-        <v>-10.7050871439129</v>
+        <v>-9.069157891863268</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.883664020756854</v>
       </c>
       <c r="E71">
-        <v>-8.4242815169107</v>
+        <v>-7.504516746634796</v>
       </c>
       <c r="F71">
-        <v>7.138600488138485</v>
+        <v>6.233187897752176</v>
       </c>
       <c r="G71">
-        <v>-10.34093706622969</v>
+        <v>-10.05757754188685</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.714428181566455</v>
       </c>
       <c r="E72">
-        <v>-8.364415090529297</v>
+        <v>-8.687322458120239</v>
       </c>
       <c r="F72">
-        <v>6.995446143030083</v>
+        <v>5.947085089304379</v>
       </c>
       <c r="G72">
-        <v>-10.76429625088277</v>
+        <v>-10.25307849816297</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.515186206664603</v>
       </c>
       <c r="E73">
-        <v>-7.334893695729487</v>
+        <v>-7.641706866697169</v>
       </c>
       <c r="F73">
-        <v>7.006384799788023</v>
+        <v>5.763275429640729</v>
       </c>
       <c r="G73">
-        <v>-10.95154732767502</v>
+        <v>-9.422316958356101</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.291699028237487</v>
       </c>
       <c r="E74">
-        <v>-8.093616873344617</v>
+        <v>-7.597124040091654</v>
       </c>
       <c r="F74">
-        <v>6.947822522446903</v>
+        <v>5.684543073760572</v>
       </c>
       <c r="G74">
-        <v>-10.5242221094659</v>
+        <v>-8.915909428304866</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.053466702474306</v>
       </c>
       <c r="E75">
-        <v>-8.792491738474375</v>
+        <v>-9.557627235284366</v>
       </c>
       <c r="F75">
-        <v>6.624303078040933</v>
+        <v>5.657160798482625</v>
       </c>
       <c r="G75">
-        <v>-9.904041060866531</v>
+        <v>-10.14145021312429</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.805602426551546</v>
       </c>
       <c r="E76">
-        <v>-9.023208432217166</v>
+        <v>-7.93713092553556</v>
       </c>
       <c r="F76">
-        <v>6.717990368880584</v>
+        <v>5.456038065751392</v>
       </c>
       <c r="G76">
-        <v>-9.520276000863136</v>
+        <v>-9.080281324875219</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.555528543365833</v>
       </c>
       <c r="E77">
-        <v>-8.965366233717191</v>
+        <v>-10.14348044613069</v>
       </c>
       <c r="F77">
-        <v>6.684941593837194</v>
+        <v>5.423713044311357</v>
       </c>
       <c r="G77">
-        <v>-10.15782748190706</v>
+        <v>-8.88432351331468</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.30512824722978</v>
       </c>
       <c r="E78">
-        <v>-9.62688118828367</v>
+        <v>-10.25832707543922</v>
       </c>
       <c r="F78">
-        <v>6.68887393562523</v>
+        <v>5.482815365369643</v>
       </c>
       <c r="G78">
-        <v>-10.07004836693328</v>
+        <v>-9.825359325034672</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.057797174955375</v>
       </c>
       <c r="E79">
-        <v>-9.420174463729548</v>
+        <v>-9.92493176204651</v>
       </c>
       <c r="F79">
-        <v>6.48659034645798</v>
+        <v>5.395919005495395</v>
       </c>
       <c r="G79">
-        <v>-9.973264568092691</v>
+        <v>-8.969566750405374</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.81149677918838</v>
       </c>
       <c r="E80">
-        <v>-10.89935521359499</v>
+        <v>-10.22786855926363</v>
       </c>
       <c r="F80">
-        <v>6.477723177037435</v>
+        <v>5.502695625726154</v>
       </c>
       <c r="G80">
-        <v>-9.987638956824206</v>
+        <v>-8.532233753031033</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.566548078808384</v>
       </c>
       <c r="E81">
-        <v>-10.9416330469306</v>
+        <v>-10.61609916441521</v>
       </c>
       <c r="F81">
-        <v>6.927772805557439</v>
+        <v>4.928271236843027</v>
       </c>
       <c r="G81">
-        <v>-10.00289726121471</v>
+        <v>-9.283767316992064</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.319666007994421</v>
       </c>
       <c r="E82">
-        <v>-11.6683987834736</v>
+        <v>-11.71443072176157</v>
       </c>
       <c r="F82">
-        <v>6.553088574141367</v>
+        <v>5.246372823312279</v>
       </c>
       <c r="G82">
-        <v>-8.975469453101894</v>
+        <v>-8.562353096347321</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.070769899710541</v>
       </c>
       <c r="E83">
-        <v>-12.96471522443531</v>
+        <v>-11.46007086522474</v>
       </c>
       <c r="F83">
-        <v>6.644471572874054</v>
+        <v>5.452287850143631</v>
       </c>
       <c r="G83">
-        <v>-9.987602540823275</v>
+        <v>-8.151825586204458</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.817192825385973</v>
       </c>
       <c r="E84">
-        <v>-14.22987123575024</v>
+        <v>-12.93799269931605</v>
       </c>
       <c r="F84">
-        <v>6.721615471721025</v>
+        <v>5.120840373924971</v>
       </c>
       <c r="G84">
-        <v>-9.005982751337356</v>
+        <v>-7.732237112920611</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.559742359256131</v>
       </c>
       <c r="E85">
-        <v>-15.73349668830909</v>
+        <v>-15.1056826373077</v>
       </c>
       <c r="F85">
-        <v>6.470574328535141</v>
+        <v>5.69089215077557</v>
       </c>
       <c r="G85">
-        <v>-8.595084460094096</v>
+        <v>-7.342559418584078</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.297313404082451</v>
       </c>
       <c r="E86">
-        <v>-16.38547920508942</v>
+        <v>-15.5841340301141</v>
       </c>
       <c r="F86">
-        <v>6.747352276552832</v>
+        <v>5.340270747038684</v>
       </c>
       <c r="G86">
-        <v>-8.558638664252259</v>
+        <v>-6.486972097778215</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.032854570429368</v>
       </c>
       <c r="E87">
-        <v>-16.89896287281917</v>
+        <v>-15.93177592273494</v>
       </c>
       <c r="F87">
-        <v>6.422629215651128</v>
+        <v>5.209380620539444</v>
       </c>
       <c r="G87">
-        <v>-8.117673998421337</v>
+        <v>-7.31820373505166</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.768694520611554</v>
       </c>
       <c r="E88">
-        <v>-18.00228028004797</v>
+        <v>-17.04246115717423</v>
       </c>
       <c r="F88">
-        <v>6.282333459720093</v>
+        <v>4.652462516845586</v>
       </c>
       <c r="G88">
-        <v>-7.455710554570827</v>
+        <v>-5.823644709165525</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.511277835835777</v>
       </c>
       <c r="E89">
-        <v>-19.52297807961574</v>
+        <v>-20.72369390580152</v>
       </c>
       <c r="F89">
-        <v>6.636709830182485</v>
+        <v>5.067536000223111</v>
       </c>
       <c r="G89">
-        <v>-7.351918330823597</v>
+        <v>-5.985861440589813</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.265267449503001</v>
       </c>
       <c r="E90">
-        <v>-21.03912023433179</v>
+        <v>-21.3452994189384</v>
       </c>
       <c r="F90">
-        <v>6.098395519877294</v>
+        <v>5.058258650970466</v>
       </c>
       <c r="G90">
-        <v>-7.069561901779158</v>
+        <v>-6.250566040818859</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.036752008415339</v>
       </c>
       <c r="E91">
-        <v>-22.88368996645413</v>
+        <v>-23.29219002126406</v>
       </c>
       <c r="F91">
-        <v>5.953432582613459</v>
+        <v>5.086895221333442</v>
       </c>
       <c r="G91">
-        <v>-6.452446418349155</v>
+        <v>-5.86591375461094</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.8281667149161731</v>
       </c>
       <c r="E92">
-        <v>-24.83695666018259</v>
+        <v>-24.42103896494811</v>
       </c>
       <c r="F92">
-        <v>6.262413606715696</v>
+        <v>4.621263510311429</v>
       </c>
       <c r="G92">
-        <v>-6.797170214807925</v>
+        <v>-4.800424604433126</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6421206193345979</v>
       </c>
       <c r="E93">
-        <v>-26.52379058566976</v>
+        <v>-26.47455701625837</v>
       </c>
       <c r="F93">
-        <v>5.828055336405865</v>
+        <v>4.859939077709561</v>
       </c>
       <c r="G93">
-        <v>-6.351977982323353</v>
+        <v>-4.445196446978249</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4777711303216036</v>
       </c>
       <c r="E94">
-        <v>-28.32774443441731</v>
+        <v>-28.91016053349181</v>
       </c>
       <c r="F94">
-        <v>5.650075298216949</v>
+        <v>4.455981626152506</v>
       </c>
       <c r="G94">
-        <v>-4.920759624240095</v>
+        <v>-4.533746919062675</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.3340730330826155</v>
       </c>
       <c r="E95">
-        <v>-30.55433170535272</v>
+        <v>-30.80330947053143</v>
       </c>
       <c r="F95">
-        <v>5.53695435208894</v>
+        <v>4.165981317446811</v>
       </c>
       <c r="G95">
-        <v>-5.113476411717688</v>
+        <v>-4.118488639344194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2074260135028766</v>
       </c>
       <c r="E96">
-        <v>-32.81125748790251</v>
+        <v>-33.21185761980605</v>
       </c>
       <c r="F96">
-        <v>5.166430516112727</v>
+        <v>3.571231646844935</v>
       </c>
       <c r="G96">
-        <v>-4.712473341091308</v>
+        <v>-4.661391623420354</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.09315308518543364</v>
       </c>
       <c r="E97">
-        <v>-35.11356310848317</v>
+        <v>-35.0113871494481</v>
       </c>
       <c r="F97">
-        <v>4.76459206307053</v>
+        <v>3.863818147310542</v>
       </c>
       <c r="G97">
-        <v>-4.63111006337264</v>
+        <v>-4.033977032817678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.01363707155621027</v>
       </c>
       <c r="E98">
-        <v>-37.19643472831115</v>
+        <v>-36.91983780015965</v>
       </c>
       <c r="F98">
-        <v>4.486962081270333</v>
+        <v>3.142265895177176</v>
       </c>
       <c r="G98">
-        <v>-4.5915953918159</v>
+        <v>-3.322461343335358</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.1184193762295042</v>
       </c>
       <c r="E99">
-        <v>-39.31200193047451</v>
+        <v>-40.74381937069374</v>
       </c>
       <c r="F99">
-        <v>4.32400666110119</v>
+        <v>3.011505632563002</v>
       </c>
       <c r="G99">
-        <v>-3.914817256677151</v>
+        <v>-3.026991843409865</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.2225709493018213</v>
       </c>
       <c r="E100">
-        <v>-42.19159741755299</v>
+        <v>-42.02988787497608</v>
       </c>
       <c r="F100">
-        <v>3.923424086849937</v>
+        <v>2.722686768470226</v>
       </c>
       <c r="G100">
-        <v>-4.036983008167337</v>
+        <v>-4.867562467969545</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.3293867205806916</v>
       </c>
       <c r="E101">
-        <v>-44.44710125926437</v>
+        <v>-44.14486863975545</v>
       </c>
       <c r="F101">
-        <v>3.529078146493684</v>
+        <v>2.667618146378565</v>
       </c>
       <c r="G101">
-        <v>-3.926973579897355</v>
+        <v>-3.350564564418231</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4335029170541797</v>
       </c>
       <c r="E102">
-        <v>-46.05877383740923</v>
+        <v>-48.14154583080905</v>
       </c>
       <c r="F102">
-        <v>3.37492654750847</v>
+        <v>1.831643141854699</v>
       </c>
       <c r="G102">
-        <v>-4.144294341822812</v>
+        <v>-3.579591415370551</v>
       </c>
     </row>
   </sheetData>
